--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-test-results.xlsx
+++ b/branches/master/StructureDefinition-hiv-test-results.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
